--- a/templates/_masters/SPC-002-corporate-housing-travel-nurse-tracker-DEMO.xlsx
+++ b/templates/_masters/SPC-002-corporate-housing-travel-nurse-tracker-DEMO.xlsx
@@ -596,7 +596,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="6">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -621,14 +621,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00FFE4CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00FFD6D6"/>
+          <fgColor rgb="00FFCCCC"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4273,13 +4266,13 @@
     <cfRule type="expression" priority="3" dxfId="2">
       <formula>N6="Lead"</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" dxfId="3">
+    <cfRule type="expression" priority="4" dxfId="1">
       <formula>N6="Application"</formula>
     </cfRule>
-    <cfRule type="expression" priority="5" dxfId="4">
+    <cfRule type="expression" priority="5" dxfId="3">
       <formula>N6="Move-out"</formula>
     </cfRule>
-    <cfRule type="expression" priority="6" dxfId="5">
+    <cfRule type="expression" priority="6" dxfId="4">
       <formula>N6="Past"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5061,10 +5054,10 @@
     <mergeCell ref="A4:L4"/>
   </mergeCells>
   <conditionalFormatting sqref="B6:M15">
-    <cfRule type="expression" priority="1" dxfId="6">
+    <cfRule type="expression" priority="1" dxfId="5">
       <formula>LEN(B6)&gt;0</formula>
     </cfRule>
-    <cfRule type="expression" priority="2" dxfId="4">
+    <cfRule type="expression" priority="2" dxfId="3">
       <formula>AND(LEN(B6)=0,LEN($A6)&gt;0)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6278,7 +6271,7 @@
     <cfRule type="cellIs" priority="1" operator="greaterThanOrEqual" dxfId="0">
       <formula>0.25</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="4">
+    <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="3">
       <formula>0.10</formula>
     </cfRule>
   </conditionalFormatting>
